--- a/seguimiento/ponedera-c9zxskjm/cronograma-ejecutado.xlsx
+++ b/seguimiento/ponedera-c9zxskjm/cronograma-ejecutado.xlsx
@@ -1301,13 +1301,13 @@
       <c r="G18" s="21" t="n"/>
       <c r="H18" s="21" t="n"/>
       <c r="I18" s="21" t="n"/>
-      <c r="J18" s="21" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="K18" s="21" t="n">
+      <c r="J18" s="21" t="n">
         <v>0.61</v>
+      </c>
+      <c r="K18" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
       </c>
       <c r="L18" s="21" t="n"/>
       <c r="M18" s="21" t="n"/>
@@ -1343,9 +1343,13 @@
       <c r="G19" s="21" t="n"/>
       <c r="H19" s="21" t="n"/>
       <c r="I19" s="21" t="n"/>
-      <c r="J19" s="21" t="n"/>
-      <c r="K19" s="21" t="n">
+      <c r="J19" s="21" t="n">
         <v>0.06</v>
+      </c>
+      <c r="K19" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
         <is>

--- a/seguimiento/ponedera-c9zxskjm/cronograma-ejecutado.xlsx
+++ b/seguimiento/ponedera-c9zxskjm/cronograma-ejecutado.xlsx
@@ -1054,7 +1054,9 @@
       <c r="H12" s="21" t="n"/>
       <c r="I12" s="21" t="n"/>
       <c r="J12" s="21" t="n"/>
-      <c r="K12" s="21" t="n"/>
+      <c r="K12" s="21" t="n">
+        <v>0.22</v>
+      </c>
       <c r="L12" s="21" t="n"/>
       <c r="M12" s="21" t="n"/>
       <c r="N12" s="21" t="n"/>
@@ -1346,10 +1348,8 @@
       <c r="J19" s="21" t="n">
         <v>0.06</v>
       </c>
-      <c r="K19" s="21" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+      <c r="K19" s="21" t="n">
+        <v>0.33</v>
       </c>
       <c r="L19" s="21" t="inlineStr">
         <is>

--- a/seguimiento/ponedera-c9zxskjm/cronograma-ejecutado.xlsx
+++ b/seguimiento/ponedera-c9zxskjm/cronograma-ejecutado.xlsx
@@ -18,11 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="dd/mm"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="dd/mm"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -127,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,7 +149,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -190,10 +189,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -687,46 +693,46 @@
           <t>SEMANA DEL</t>
         </is>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="26" t="n">
         <v>46268</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" s="26" t="n">
         <v>46275</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="26" t="n">
         <v>46282</v>
       </c>
-      <c r="H5" s="10" t="n">
+      <c r="H5" s="26" t="n">
         <v>46289</v>
       </c>
-      <c r="I5" s="10" t="n">
+      <c r="I5" s="26" t="n">
         <v>46296</v>
       </c>
-      <c r="J5" s="10" t="n">
+      <c r="J5" s="26" t="n">
         <v>46303</v>
       </c>
-      <c r="K5" s="10" t="n">
+      <c r="K5" s="26" t="n">
         <v>46310</v>
       </c>
-      <c r="L5" s="10" t="n">
+      <c r="L5" s="26" t="n">
         <v>46317</v>
       </c>
-      <c r="M5" s="10" t="n">
+      <c r="M5" s="26" t="n">
         <v>46324</v>
       </c>
-      <c r="N5" s="10" t="n">
+      <c r="N5" s="26" t="n">
         <v>46331</v>
       </c>
-      <c r="O5" s="10" t="n">
+      <c r="O5" s="26" t="n">
         <v>46338</v>
       </c>
-      <c r="P5" s="10" t="n">
+      <c r="P5" s="26" t="n">
         <v>46345</v>
       </c>
-      <c r="Q5" s="10" t="n">
+      <c r="Q5" s="26" t="n">
         <v>46352</v>
       </c>
-      <c r="R5" s="10" t="n">
+      <c r="R5" s="26" t="n">
         <v>46359</v>
       </c>
     </row>
@@ -1057,8 +1063,16 @@
       <c r="K12" s="21" t="n">
         <v>0.22</v>
       </c>
-      <c r="L12" s="21" t="n"/>
-      <c r="M12" s="21" t="n"/>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M12" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="N12" s="21" t="n"/>
       <c r="O12" s="21" t="n"/>
       <c r="P12" s="21" t="n"/>
@@ -1311,7 +1325,11 @@
           <t>P</t>
         </is>
       </c>
-      <c r="L18" s="21" t="n"/>
+      <c r="L18" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="M18" s="21" t="n"/>
       <c r="N18" s="21" t="n"/>
       <c r="O18" s="21" t="n"/>
@@ -1356,7 +1374,11 @@
           <t>P</t>
         </is>
       </c>
-      <c r="M19" s="21" t="n"/>
+      <c r="M19" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="N19" s="21" t="n"/>
       <c r="O19" s="21" t="n"/>
       <c r="P19" s="21" t="n"/>
@@ -1761,9 +1783,21 @@
       <c r="I28" s="21" t="n"/>
       <c r="J28" s="21" t="n"/>
       <c r="K28" s="21" t="n"/>
-      <c r="L28" s="21" t="n"/>
-      <c r="M28" s="21" t="n"/>
-      <c r="N28" s="21" t="n"/>
+      <c r="L28" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M28" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="N28" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="O28" s="21" t="n"/>
       <c r="P28" s="21" t="n"/>
       <c r="Q28" s="21" t="n"/>
@@ -1848,7 +1882,11 @@
       <c r="L30" s="21" t="n"/>
       <c r="M30" s="21" t="n"/>
       <c r="N30" s="21" t="n"/>
-      <c r="O30" s="21" t="n"/>
+      <c r="O30" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="P30" s="21" t="n"/>
       <c r="Q30" s="21" t="n"/>
       <c r="R30" s="21" t="n"/>
@@ -2727,7 +2765,11 @@
           <t>P</t>
         </is>
       </c>
-      <c r="N51" s="21" t="n"/>
+      <c r="N51" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="O51" s="21" t="n"/>
       <c r="P51" s="21" t="n"/>
       <c r="Q51" s="21" t="n"/>
@@ -3745,7 +3787,11 @@
           <t>P</t>
         </is>
       </c>
-      <c r="L76" s="21" t="n"/>
+      <c r="L76" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="M76" s="21" t="n"/>
       <c r="N76" s="21" t="n"/>
       <c r="O76" s="21" t="n"/>
@@ -3790,7 +3836,11 @@
           <t>P</t>
         </is>
       </c>
-      <c r="M77" s="21" t="n"/>
+      <c r="M77" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="N77" s="21" t="n"/>
       <c r="O77" s="21" t="n"/>
       <c r="P77" s="21" t="n"/>
@@ -3834,7 +3884,11 @@
           <t>P</t>
         </is>
       </c>
-      <c r="M78" s="21" t="n"/>
+      <c r="M78" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="N78" s="21" t="n"/>
       <c r="O78" s="21" t="n"/>
       <c r="P78" s="21" t="n"/>
@@ -3878,7 +3932,11 @@
           <t>P</t>
         </is>
       </c>
-      <c r="M79" s="21" t="n"/>
+      <c r="M79" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="N79" s="21" t="n"/>
       <c r="O79" s="21" t="n"/>
       <c r="P79" s="21" t="n"/>
@@ -3917,7 +3975,11 @@
           <t>P</t>
         </is>
       </c>
-      <c r="L80" s="21" t="n"/>
+      <c r="L80" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="M80" s="21" t="n"/>
       <c r="N80" s="21" t="n"/>
       <c r="O80" s="21" t="n"/>
@@ -3957,7 +4019,11 @@
           <t>P</t>
         </is>
       </c>
-      <c r="L81" s="21" t="n"/>
+      <c r="L81" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="M81" s="21" t="n"/>
       <c r="N81" s="21" t="n"/>
       <c r="O81" s="21" t="n"/>
@@ -3997,7 +4063,11 @@
           <t>P</t>
         </is>
       </c>
-      <c r="L82" s="21" t="n"/>
+      <c r="L82" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="M82" s="21" t="n"/>
       <c r="N82" s="21" t="n"/>
       <c r="O82" s="21" t="n"/>
@@ -4037,7 +4107,11 @@
           <t>P</t>
         </is>
       </c>
-      <c r="L83" s="21" t="n"/>
+      <c r="L83" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="M83" s="21" t="n"/>
       <c r="N83" s="21" t="n"/>
       <c r="O83" s="21" t="n"/>
@@ -4077,7 +4151,11 @@
           <t>P</t>
         </is>
       </c>
-      <c r="L84" s="21" t="n"/>
+      <c r="L84" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="M84" s="21" t="n"/>
       <c r="N84" s="21" t="n"/>
       <c r="O84" s="21" t="n"/>
@@ -4117,7 +4195,11 @@
           <t>P</t>
         </is>
       </c>
-      <c r="L85" s="21" t="n"/>
+      <c r="L85" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="M85" s="21" t="n"/>
       <c r="N85" s="21" t="n"/>
       <c r="O85" s="21" t="n"/>
@@ -4199,7 +4281,11 @@
           <t>P</t>
         </is>
       </c>
-      <c r="N87" s="21" t="n"/>
+      <c r="N87" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="O87" s="21" t="n"/>
       <c r="P87" s="21" t="n"/>
       <c r="Q87" s="21" t="n"/>
@@ -4242,7 +4328,11 @@
           <t>P</t>
         </is>
       </c>
-      <c r="M88" s="21" t="n"/>
+      <c r="M88" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="N88" s="21" t="n"/>
       <c r="O88" s="21" t="n"/>
       <c r="P88" s="21" t="n"/>
@@ -4281,7 +4371,11 @@
           <t>P</t>
         </is>
       </c>
-      <c r="L89" s="21" t="n"/>
+      <c r="L89" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="M89" s="21" t="n"/>
       <c r="N89" s="21" t="n"/>
       <c r="O89" s="21" t="n"/>
@@ -4326,7 +4420,11 @@
           <t>P</t>
         </is>
       </c>
-      <c r="M90" s="21" t="n"/>
+      <c r="M90" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="N90" s="21" t="n"/>
       <c r="O90" s="21" t="n"/>
       <c r="P90" s="21" t="n"/>
@@ -4365,7 +4463,11 @@
           <t>P</t>
         </is>
       </c>
-      <c r="L91" s="21" t="n"/>
+      <c r="L91" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="M91" s="21" t="n"/>
       <c r="N91" s="21" t="n"/>
       <c r="O91" s="21" t="n"/>
@@ -6053,7 +6155,11 @@
       <c r="M133" s="21" t="n"/>
       <c r="N133" s="21" t="n"/>
       <c r="O133" s="21" t="n"/>
-      <c r="P133" s="21" t="n"/>
+      <c r="P133" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Q133" s="21" t="n"/>
       <c r="R133" s="21" t="n"/>
       <c r="S133" s="22">
@@ -6093,7 +6199,11 @@
       <c r="M134" s="21" t="n"/>
       <c r="N134" s="21" t="n"/>
       <c r="O134" s="21" t="n"/>
-      <c r="P134" s="21" t="n"/>
+      <c r="P134" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Q134" s="21" t="n"/>
       <c r="R134" s="21" t="n"/>
       <c r="S134" s="22">
@@ -6133,7 +6243,11 @@
       <c r="M135" s="21" t="n"/>
       <c r="N135" s="21" t="n"/>
       <c r="O135" s="21" t="n"/>
-      <c r="P135" s="21" t="n"/>
+      <c r="P135" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Q135" s="21" t="n"/>
       <c r="R135" s="21" t="n"/>
       <c r="S135" s="22">
@@ -6173,7 +6287,11 @@
       <c r="M136" s="21" t="n"/>
       <c r="N136" s="21" t="n"/>
       <c r="O136" s="21" t="n"/>
-      <c r="P136" s="21" t="n"/>
+      <c r="P136" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Q136" s="21" t="n"/>
       <c r="R136" s="21" t="n"/>
       <c r="S136" s="22">
@@ -6213,7 +6331,11 @@
       <c r="M137" s="21" t="n"/>
       <c r="N137" s="21" t="n"/>
       <c r="O137" s="21" t="n"/>
-      <c r="P137" s="21" t="n"/>
+      <c r="P137" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Q137" s="21" t="n"/>
       <c r="R137" s="21" t="n"/>
       <c r="S137" s="22">
@@ -6253,7 +6375,11 @@
       <c r="M138" s="21" t="n"/>
       <c r="N138" s="21" t="n"/>
       <c r="O138" s="21" t="n"/>
-      <c r="P138" s="21" t="n"/>
+      <c r="P138" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Q138" s="21" t="n"/>
       <c r="R138" s="21" t="n"/>
       <c r="S138" s="22">
@@ -6325,7 +6451,11 @@
       <c r="M140" s="21" t="n"/>
       <c r="N140" s="21" t="n"/>
       <c r="O140" s="21" t="n"/>
-      <c r="P140" s="21" t="n"/>
+      <c r="P140" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Q140" s="21" t="n"/>
       <c r="R140" s="21" t="n"/>
       <c r="S140" s="22">
@@ -6369,8 +6499,16 @@
       <c r="M141" s="21" t="n"/>
       <c r="N141" s="21" t="n"/>
       <c r="O141" s="21" t="n"/>
-      <c r="P141" s="21" t="n"/>
-      <c r="Q141" s="21" t="n"/>
+      <c r="P141" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Q141" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="R141" s="21" t="n"/>
       <c r="S141" s="22">
         <f>SUM(E141:R141)</f>
@@ -6410,7 +6548,11 @@
       <c r="N142" s="21" t="n"/>
       <c r="O142" s="21" t="n"/>
       <c r="P142" s="21" t="n"/>
-      <c r="Q142" s="21" t="n"/>
+      <c r="Q142" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="R142" s="21" t="n"/>
       <c r="S142" s="22">
         <f>SUM(E142:R142)</f>
@@ -6450,7 +6592,11 @@
       <c r="N143" s="21" t="n"/>
       <c r="O143" s="21" t="n"/>
       <c r="P143" s="21" t="n"/>
-      <c r="Q143" s="21" t="n"/>
+      <c r="Q143" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="R143" s="21" t="n"/>
       <c r="S143" s="22">
         <f>SUM(E143:R143)</f>
@@ -6490,7 +6636,11 @@
       <c r="N144" s="21" t="n"/>
       <c r="O144" s="21" t="n"/>
       <c r="P144" s="21" t="n"/>
-      <c r="Q144" s="21" t="n"/>
+      <c r="Q144" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="R144" s="21" t="n"/>
       <c r="S144" s="22">
         <f>SUM(E144:R144)</f>
@@ -6530,7 +6680,11 @@
       <c r="N145" s="21" t="n"/>
       <c r="O145" s="21" t="n"/>
       <c r="P145" s="21" t="n"/>
-      <c r="Q145" s="21" t="n"/>
+      <c r="Q145" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="R145" s="21" t="n"/>
       <c r="S145" s="22">
         <f>SUM(E145:R145)</f>
@@ -6570,7 +6724,11 @@
       <c r="N146" s="21" t="n"/>
       <c r="O146" s="21" t="n"/>
       <c r="P146" s="21" t="n"/>
-      <c r="Q146" s="21" t="n"/>
+      <c r="Q146" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="R146" s="21" t="n"/>
       <c r="S146" s="22">
         <f>SUM(E146:R146)</f>
@@ -6610,7 +6768,11 @@
       <c r="N147" s="21" t="n"/>
       <c r="O147" s="21" t="n"/>
       <c r="P147" s="21" t="n"/>
-      <c r="Q147" s="21" t="n"/>
+      <c r="Q147" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="R147" s="21" t="n"/>
       <c r="S147" s="22">
         <f>SUM(E147:R147)</f>
@@ -6693,65 +6855,66 @@
         <v/>
       </c>
     </row>
+    <row r="150"/>
     <row r="151">
       <c r="B151" s="23" t="inlineStr">
         <is>
           <t>% AVANCE EJECUTADO SEMANAL</t>
         </is>
       </c>
-      <c r="E151" s="24">
+      <c r="E151" s="27">
         <f>SUMPRODUCT($C$7:$C$149,E7:E149)</f>
         <v/>
       </c>
-      <c r="F151" s="24">
+      <c r="F151" s="27">
         <f>SUMPRODUCT($C$7:$C$149,F7:F149)</f>
         <v/>
       </c>
-      <c r="G151" s="24">
+      <c r="G151" s="27">
         <f>SUMPRODUCT($C$7:$C$149,G7:G149)</f>
         <v/>
       </c>
-      <c r="H151" s="24">
+      <c r="H151" s="27">
         <f>SUMPRODUCT($C$7:$C$149,H7:H149)</f>
         <v/>
       </c>
-      <c r="I151" s="24">
+      <c r="I151" s="27">
         <f>SUMPRODUCT($C$7:$C$149,I7:I149)</f>
         <v/>
       </c>
-      <c r="J151" s="24">
+      <c r="J151" s="27">
         <f>SUMPRODUCT($C$7:$C$149,J7:J149)</f>
         <v/>
       </c>
-      <c r="K151" s="24">
+      <c r="K151" s="27">
         <f>SUMPRODUCT($C$7:$C$149,K7:K149)</f>
         <v/>
       </c>
-      <c r="L151" s="24">
+      <c r="L151" s="27">
         <f>SUMPRODUCT($C$7:$C$149,L7:L149)</f>
         <v/>
       </c>
-      <c r="M151" s="24">
+      <c r="M151" s="27">
         <f>SUMPRODUCT($C$7:$C$149,M7:M149)</f>
         <v/>
       </c>
-      <c r="N151" s="24">
+      <c r="N151" s="27">
         <f>SUMPRODUCT($C$7:$C$149,N7:N149)</f>
         <v/>
       </c>
-      <c r="O151" s="24">
+      <c r="O151" s="27">
         <f>SUMPRODUCT($C$7:$C$149,O7:O149)</f>
         <v/>
       </c>
-      <c r="P151" s="24">
+      <c r="P151" s="27">
         <f>SUMPRODUCT($C$7:$C$149,P7:P149)</f>
         <v/>
       </c>
-      <c r="Q151" s="24">
+      <c r="Q151" s="27">
         <f>SUMPRODUCT($C$7:$C$149,Q7:Q149)</f>
         <v/>
       </c>
-      <c r="R151" s="24">
+      <c r="R151" s="27">
         <f>SUMPRODUCT($C$7:$C$149,R7:R149)</f>
         <v/>
       </c>
@@ -6762,63 +6925,63 @@
           <t>% AVANCE EJECUTADO ACUMULADO</t>
         </is>
       </c>
-      <c r="E152" s="24">
+      <c r="E152" s="27">
         <f>E151</f>
         <v/>
       </c>
-      <c r="F152" s="24">
+      <c r="F152" s="27">
         <f>E152+F151</f>
         <v/>
       </c>
-      <c r="G152" s="24">
+      <c r="G152" s="27">
         <f>F152+G151</f>
         <v/>
       </c>
-      <c r="H152" s="24">
+      <c r="H152" s="27">
         <f>G152+H151</f>
         <v/>
       </c>
-      <c r="I152" s="24">
+      <c r="I152" s="27">
         <f>H152+I151</f>
         <v/>
       </c>
-      <c r="J152" s="24">
+      <c r="J152" s="27">
         <f>I152+J151</f>
         <v/>
       </c>
-      <c r="K152" s="24">
+      <c r="K152" s="27">
         <f>J152+K151</f>
         <v/>
       </c>
-      <c r="L152" s="24">
+      <c r="L152" s="27">
         <f>K152+L151</f>
         <v/>
       </c>
-      <c r="M152" s="24">
+      <c r="M152" s="27">
         <f>L152+M151</f>
         <v/>
       </c>
-      <c r="N152" s="24">
+      <c r="N152" s="27">
         <f>M152+N151</f>
         <v/>
       </c>
-      <c r="O152" s="24">
+      <c r="O152" s="27">
         <f>N152+O151</f>
         <v/>
       </c>
-      <c r="P152" s="24">
+      <c r="P152" s="27">
         <f>O152+P151</f>
         <v/>
       </c>
-      <c r="Q152" s="24">
+      <c r="Q152" s="27">
         <f>P152+Q151</f>
         <v/>
       </c>
-      <c r="R152" s="24">
+      <c r="R152" s="27">
         <f>Q152+R151</f>
         <v/>
       </c>
-      <c r="S152" s="25">
+      <c r="S152" s="28">
         <f>MAX(E152:R152)</f>
         <v/>
       </c>
@@ -6829,46 +6992,46 @@
           <t>% AVANCE PROGRAMADO SEMANAL (LÍNEA BASE)</t>
         </is>
       </c>
-      <c r="E153" s="24" t="n">
+      <c r="E153" s="27" t="n">
         <v>0.005432798387048396</v>
       </c>
-      <c r="F153" s="24" t="n">
+      <c r="F153" s="27" t="n">
         <v>0.02552941367600974</v>
       </c>
-      <c r="G153" s="24" t="n">
+      <c r="G153" s="27" t="n">
         <v>0.03441555124643336</v>
       </c>
-      <c r="H153" s="24" t="n">
+      <c r="H153" s="27" t="n">
         <v>0.04139908168083772</v>
       </c>
-      <c r="I153" s="24" t="n">
+      <c r="I153" s="27" t="n">
         <v>0.09522379269756046</v>
       </c>
-      <c r="J153" s="24" t="n">
+      <c r="J153" s="27" t="n">
         <v>0.02330448829793537</v>
       </c>
-      <c r="K153" s="24" t="n">
+      <c r="K153" s="27" t="n">
         <v>0.06577207393114769</v>
       </c>
-      <c r="L153" s="24" t="n">
+      <c r="L153" s="27" t="n">
         <v>0.100233321333762</v>
       </c>
-      <c r="M153" s="24" t="n">
+      <c r="M153" s="27" t="n">
         <v>0.08711177209645567</v>
       </c>
-      <c r="N153" s="24" t="n">
+      <c r="N153" s="27" t="n">
         <v>0.1370548039853123</v>
       </c>
-      <c r="O153" s="24" t="n">
+      <c r="O153" s="27" t="n">
         <v>0.2111435747304669</v>
       </c>
-      <c r="P153" s="24" t="n">
+      <c r="P153" s="27" t="n">
         <v>0.1592412900418003</v>
       </c>
-      <c r="Q153" s="24" t="n">
+      <c r="Q153" s="27" t="n">
         <v>0.01259328633396554</v>
       </c>
-      <c r="R153" s="24" t="n">
+      <c r="R153" s="27" t="n">
         <v>0.001544751561264538</v>
       </c>
     </row>
@@ -6878,46 +7041,46 @@
           <t>% AVANCE PROGRAMADO ACUMULADO (LÍNEA BASE)</t>
         </is>
       </c>
-      <c r="E154" s="24" t="n">
+      <c r="E154" s="27" t="n">
         <v>0.005432798387048396</v>
       </c>
-      <c r="F154" s="24" t="n">
+      <c r="F154" s="27" t="n">
         <v>0.03096221206305814</v>
       </c>
-      <c r="G154" s="24" t="n">
+      <c r="G154" s="27" t="n">
         <v>0.06537776330949149</v>
       </c>
-      <c r="H154" s="24" t="n">
+      <c r="H154" s="27" t="n">
         <v>0.1067768449903292</v>
       </c>
-      <c r="I154" s="24" t="n">
+      <c r="I154" s="27" t="n">
         <v>0.2020006376878897</v>
       </c>
-      <c r="J154" s="24" t="n">
+      <c r="J154" s="27" t="n">
         <v>0.225305125985825</v>
       </c>
-      <c r="K154" s="24" t="n">
+      <c r="K154" s="27" t="n">
         <v>0.2910771999169727</v>
       </c>
-      <c r="L154" s="24" t="n">
+      <c r="L154" s="27" t="n">
         <v>0.3913105212507347</v>
       </c>
-      <c r="M154" s="24" t="n">
+      <c r="M154" s="27" t="n">
         <v>0.4784222933471904</v>
       </c>
-      <c r="N154" s="24" t="n">
+      <c r="N154" s="27" t="n">
         <v>0.6154770973325027</v>
       </c>
-      <c r="O154" s="24" t="n">
+      <c r="O154" s="27" t="n">
         <v>0.8266206720629696</v>
       </c>
-      <c r="P154" s="24" t="n">
+      <c r="P154" s="27" t="n">
         <v>0.98586196210477</v>
       </c>
-      <c r="Q154" s="24" t="n">
+      <c r="Q154" s="27" t="n">
         <v>0.9984552484387355</v>
       </c>
-      <c r="R154" s="24" t="n">
+      <c r="R154" s="27" t="n">
         <v>1</v>
       </c>
     </row>
